--- a/SmartAutoVision/Config/NewKeys.xlsx
+++ b/SmartAutoVision/Config/NewKeys.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="198">
   <si>
     <t xml:space="preserve">Key</t>
   </si>
@@ -597,6 +597,15 @@
   </si>
   <si>
     <t xml:space="preserve">读机械位置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图像窗体</t>
+  </si>
+  <si>
+    <t xml:space="preserve">启动项目成功！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StartRun,F:\项目\SmartAutoVision\Core\Project\Project.cs,621 line</t>
   </si>
 </sst>
 </file>
@@ -2033,6 +2042,28 @@
         <v>11</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>195</v>
+      </c>
+      <c r="B127" t="s">
+        <v>85</v>
+      </c>
+      <c r="C127" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>196</v>
+      </c>
+      <c r="B128" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" t="s">
+        <v>197</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SmartAutoVision/Config/NewKeys.xlsx
+++ b/SmartAutoVision/Config/NewKeys.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="274">
   <si>
     <t xml:space="preserve">Key</t>
   </si>
@@ -578,34 +578,262 @@
     <t xml:space="preserve">学习模板</t>
   </si>
   <si>
+    <t xml:space="preserve">用户名与密码不匹配！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VerifyUser,F:\项目\Libraries\Class\Common\User\User.cs,104 line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">启动项目成功！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StartRun,F:\项目\SmartAutoVision\Core\Project\Project.cs,621 line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">打开设备失败:{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StartRun,F:\项目\SmartAutoVision\Core\Project\Project.cs,629 line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">失败</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模板区域1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">搜索区域1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是否固定相机</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plugin.CalibHandEye.ToolCalibHandEye,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">圆心检查值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">读取距离</t>
+  </si>
+  <si>
+    <t xml:space="preserve">写入结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">方向判断</t>
+  </si>
+  <si>
+    <t xml:space="preserve">写PLC结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark点间标定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电芯坐标转换</t>
+  </si>
+  <si>
+    <t xml:space="preserve">写入坐标结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">读取坐标</t>
+  </si>
+  <si>
+    <t xml:space="preserve">慎用:计算电芯补偿1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">慎用:计算泡棉补偿1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">慎用:计算电芯补偿2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">慎用:计算泡棉补偿2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">读取PLC坐标</t>
+  </si>
+  <si>
+    <t xml:space="preserve">慎用:计算电芯补偿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">慎用:计算泡棉补偿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">初始化信号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">复位信号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">读坐标</t>
+  </si>
+  <si>
+    <t xml:space="preserve">横手眼标定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">横标准定位坐标赋值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">方向识别拍照</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark点拍照</t>
+  </si>
+  <si>
+    <t xml:space="preserve">横Mark点拍照</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图像[方向识别拍照]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图像[Mark点拍照]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图像[横Mark点拍照]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图像[横电芯拍照]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">测距</t>
+  </si>
+  <si>
+    <t xml:space="preserve">横电芯拍照</t>
+  </si>
+  <si>
+    <t xml:space="preserve">横写三轴坐标</t>
+  </si>
+  <si>
     <t xml:space="preserve">保存系统配置成功！</t>
   </si>
   <si>
     <t xml:space="preserve">SaveSystemConfig,F:\项目\SmartAutoVision\Core\Container.cs,289 line</t>
   </si>
   <si>
-    <t xml:space="preserve">是否固定相机</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plugin.CalibHandEye.ToolCalibHandEye,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">圆心检查值</t>
-  </si>
-  <si>
-    <t xml:space="preserve">读设备位置</t>
-  </si>
-  <si>
     <t xml:space="preserve">读机械位置</t>
   </si>
   <si>
-    <t xml:space="preserve">图像窗体</t>
-  </si>
-  <si>
-    <t xml:space="preserve">启动项目成功！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StartRun,F:\项目\SmartAutoVision\Core\Project\Project.cs,621 line</t>
+    <t xml:space="preserve">模拟动作列表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device.DeviceSimulateActionManager,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">设备名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device.SimulateInfo,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">事件类型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模拟触发</t>
+  </si>
+  <si>
+    <t xml:space="preserve">任务9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">设置标准Mark点/电芯坐标点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赋值完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">设置完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手动相机标定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手动相机标定_copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动相机标定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">连接失败，请检查该IP地址是否能Ping通</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open,F:\项目\Libraries\Class\Device\000 Base\Connecor\PortTcpClient.cs,94 line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">计算赋值1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">延时时间(ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plugin.Delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plugin.Delay.ToolDelay,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动采集相机标定点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">采集完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生成采集路径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">任务11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">写自动采集相机标定点坐标</t>
+  </si>
+  <si>
+    <t xml:space="preserve">采集路径写入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">采集路径写入_copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">读取设备位置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">读取机械位置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机械位置单位转换</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图像[自动采集相机标定点]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0}事件触发:{1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnSubscribeProcessEvent,F:\项目\Libraries\Class\Common\StartMode\StarterTrig.cs,49 line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动采集相机标定点+极柱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动采集相机标定点+极柱_copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动采集相机标定点-极柱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">采集完成-写最终结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">延时1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">模拟人工定位用时</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图像[自动采集相机标定点+极柱]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">图像[自动采集相机标定点-极柱]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">任务7</t>
   </si>
 </sst>
 </file>
@@ -1992,7 +2220,7 @@
         <v>188</v>
       </c>
       <c r="B122" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="C122" t="s">
         <v>189</v>
@@ -2003,7 +2231,7 @@
         <v>190</v>
       </c>
       <c r="B123" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C123" t="s">
         <v>191</v>
@@ -2014,54 +2242,802 @@
         <v>192</v>
       </c>
       <c r="B124" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="C124" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="C125" t="s">
-        <v>11</v>
+        <v>127</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B126" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="C126" t="s">
-        <v>11</v>
+        <v>179</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B127" t="s">
         <v>85</v>
       </c>
       <c r="C127" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B128" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C128" t="s">
-        <v>197</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>199</v>
+      </c>
+      <c r="B129" t="s">
+        <v>20</v>
+      </c>
+      <c r="C129" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>200</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>201</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>202</v>
+      </c>
+      <c r="B132" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>203</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>204</v>
+      </c>
+      <c r="B134" t="s">
+        <v>52</v>
+      </c>
+      <c r="C134" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>205</v>
+      </c>
+      <c r="B135" t="s">
+        <v>54</v>
+      </c>
+      <c r="C135" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>206</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>207</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>208</v>
+      </c>
+      <c r="B138" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>209</v>
+      </c>
+      <c r="B139" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>210</v>
+      </c>
+      <c r="B140" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>211</v>
+      </c>
+      <c r="B141" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>212</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>213</v>
+      </c>
+      <c r="B143" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>214</v>
+      </c>
+      <c r="B144" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>215</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>216</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>217</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>218</v>
+      </c>
+      <c r="B148" t="s">
+        <v>20</v>
+      </c>
+      <c r="C148" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>219</v>
+      </c>
+      <c r="B149" t="s">
+        <v>18</v>
+      </c>
+      <c r="C149" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>220</v>
+      </c>
+      <c r="B150" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>221</v>
+      </c>
+      <c r="B151" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>222</v>
+      </c>
+      <c r="B152" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>223</v>
+      </c>
+      <c r="B153" t="s">
+        <v>85</v>
+      </c>
+      <c r="C153" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>224</v>
+      </c>
+      <c r="B154" t="s">
+        <v>85</v>
+      </c>
+      <c r="C154" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>225</v>
+      </c>
+      <c r="B155" t="s">
+        <v>85</v>
+      </c>
+      <c r="C155" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>226</v>
+      </c>
+      <c r="B156" t="s">
+        <v>85</v>
+      </c>
+      <c r="C156" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>227</v>
+      </c>
+      <c r="B157" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>228</v>
+      </c>
+      <c r="B158" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>229</v>
+      </c>
+      <c r="B159" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>230</v>
+      </c>
+      <c r="B160" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>232</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>233</v>
+      </c>
+      <c r="B162" t="s">
+        <v>108</v>
+      </c>
+      <c r="C162" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>235</v>
+      </c>
+      <c r="B163" t="s">
+        <v>108</v>
+      </c>
+      <c r="C163" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>237</v>
+      </c>
+      <c r="B164" t="s">
+        <v>108</v>
+      </c>
+      <c r="C164" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>238</v>
+      </c>
+      <c r="B165" t="s">
+        <v>108</v>
+      </c>
+      <c r="C165" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>239</v>
+      </c>
+      <c r="B166" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>240</v>
+      </c>
+      <c r="B167" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>241</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>242</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>243</v>
+      </c>
+      <c r="B170" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>244</v>
+      </c>
+      <c r="B171" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>245</v>
+      </c>
+      <c r="B172" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>246</v>
+      </c>
+      <c r="B173" t="s">
+        <v>85</v>
+      </c>
+      <c r="C173" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>248</v>
+      </c>
+      <c r="B174" t="s">
+        <v>18</v>
+      </c>
+      <c r="C174" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>249</v>
+      </c>
+      <c r="B175" t="s">
+        <v>250</v>
+      </c>
+      <c r="C175" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>252</v>
+      </c>
+      <c r="B176" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>253</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>254</v>
+      </c>
+      <c r="B178" t="s">
+        <v>31</v>
+      </c>
+      <c r="C178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>255</v>
+      </c>
+      <c r="B179" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>256</v>
+      </c>
+      <c r="B180" t="s">
+        <v>7</v>
+      </c>
+      <c r="C180" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>257</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>258</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>259</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>260</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>261</v>
+      </c>
+      <c r="B185" t="s">
+        <v>18</v>
+      </c>
+      <c r="C185" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>262</v>
+      </c>
+      <c r="B186" t="s">
+        <v>85</v>
+      </c>
+      <c r="C186" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>263</v>
+      </c>
+      <c r="B187" t="s">
+        <v>85</v>
+      </c>
+      <c r="C187" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>265</v>
+      </c>
+      <c r="B188" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>266</v>
+      </c>
+      <c r="B189" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>267</v>
+      </c>
+      <c r="B190" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>268</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>269</v>
+      </c>
+      <c r="B192" t="s">
+        <v>250</v>
+      </c>
+      <c r="C192" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>270</v>
+      </c>
+      <c r="B193" t="s">
+        <v>250</v>
+      </c>
+      <c r="C193" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>271</v>
+      </c>
+      <c r="B194" t="s">
+        <v>85</v>
+      </c>
+      <c r="C194" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>272</v>
+      </c>
+      <c r="B195" t="s">
+        <v>85</v>
+      </c>
+      <c r="C195" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>273</v>
+      </c>
+      <c r="B196" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
